--- a/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jade est à la maison avec papa. Le chat Minou a soif. Il miaule tout bas. Papa dit : on prend soin avec un adulte. On est doux. Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent. Papa dit : on donne le grain avec un adulte. On est doux. Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent. Papa dit : merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
+          <t>Jade est à la maison avec papa. Le chat Minou a soif. Il miaule tout bas. On prend soin avec un adulte. On est doux. Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent. On donne le grain avec un adulte. On est doux. Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent. Merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,16 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jade est à la maison avec papa. Le chat Minou a soif. Il miaule tout bas.
+papa|On prend soin avec un adulte. On est doux.
+narrateur|Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent.
+papa|On donne le grain avec un adulte. On est doux.
+narrateur|Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent.
+papa|Merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1491,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Jade donne à boire ou à manger. Comment ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1664,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Jade a été douce. Avec papa. Pour le chat, puis pour les poules.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1791,6 +1827,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Minou se lèche. Les poules picorent.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1953,6 +1994,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1971,7 +2017,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1988,6 +2034,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1315,6 +1320,7 @@
 papa|Merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1498,6 +1504,7 @@
           <t>narrateur|Jade donne à boire ou à manger. Comment ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1669,6 +1676,7 @@
           <t>narrateur|Jade a été douce. Avec papa. Pour le chat, puis pour les poules.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1832,6 +1840,7 @@
           <t>narrateur|Minou se lèche. Les poules picorent.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1999,6 +2008,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2017,7 +2027,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2041,6 +2051,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2055,7 +2079,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2242,6 +2266,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jade prend soin, chat puis poules</t>
+          <t>Deux soifs, deux soins</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Amir veut soigner deux soifs: Minou d'abord, puis les poules. Avec papa, doux, deux fois.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jade est à la maison avec papa. Le chat Minou a soif. Il miaule tout bas. On prend soin avec un adulte. On est doux. Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent. On donne le grain avec un adulte. On est doux. Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent. Merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
+          <t>La vapeur du cacao sent le matin. Elle monte en petit nuage au-dessus de la tasse. Le bois de la table est encore froid. Bois un peu, Amir. C'est chaud. Un miaulement arrive du radiateur. Minou le chat s'étire. Sa gamelle, près du buffet, est sèche. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Amir tient le bol avec papa. L'eau arrive, un filet, pas trop. Le bol se pose sans bruit. Minou lape, tout près. Il boit. Premier soin. On reste près de moi. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe et le grain. Deux poules picorent près du grillage. Leur abreuvoir est bas, presque vide. Elles aussi. Elles ont soif. Même leçon. Autre animal. On verse avec un adulte ? Oui, papa. Amir porte le seau avec papa. Le seau tape sa jambe, tout léger. Ils versent un peu d'eau. Puis un peu de grain, tout doux. Les poules viennent. On recule. Amir met les mains dans ses poches. Il ne prend pas les poules. Deux soins. Chat, puis poules.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jade est à la maison &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Le chat Minou a soif. Il miaule tout bas. Papa dit : on prend soin avec un adulte. On est doux. Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent. Papa dit : on donne le grain avec un adulte. On est doux. Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent. Papa dit : merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La vapeur du cacao sent le matin. Elle monte en petit nuage au-dessus de la tasse. Le bois de la table est encore froid. Bois un peu, Amir. C'est chaud. Un miaulement arrive du radiateur. Minou le chat s'étire. Sa gamelle, près du buffet, est sèche. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Amir tient le bol avec papa. L'eau arrive, un filet, pas trop. Le bol se pose sans bruit. Minou lape, tout près. Il boit. Premier soin. On reste près de moi. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe et le grain. Deux poules picorent près du grillage. Leur abreuvoir est bas, presque vide. Elles aussi. Elles ont soif. Même leçon. Autre animal. On verse avec un adulte ? Oui, papa. Amir porte le seau avec papa. Le seau tape sa jambe, tout léger. Ils versent un peu d'eau. Puis un peu de grain, tout doux. Les poules viennent. On recule. Amir met les mains dans ses poches. Il ne prend pas les poules. Deux soins. Chat, puis poules.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.96</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,15 +1324,48 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jade est à la maison avec papa. Le chat Minou a soif. Il miaule tout bas.
-papa|On prend soin avec un adulte. On est doux.
-narrateur|Jade va vers papa. Ils remplissent l'eau ensemble. L'eau fait un bruit doux. Jade pose le bol, tout doux. Minou lape. Plus tard, au jardin, les poules picorent.
-papa|On donne le grain avec un adulte. On est doux.
-narrateur|Jade se souvient. Elle reste près de papa. Elle verse le grain, tout doux. Les poules viennent.
-papa|Merci d'être douce. Même leçon, autre animal. Eau ou nourriture, avec un adulte. On est doux.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La vapeur du cacao sent le matin.
+narrateur|Elle monte en petit nuage au-dessus de la tasse.
+narrateur|Le bois de la table est encore froid.
+papa|Bois un peu, Amir.
+enfant-m|C'est chaud.
+narrateur|Un miaulement arrive du radiateur.
+narrateur|Minou le chat s'étire.
+narrateur|Sa gamelle, près du buffet, est sèche.
+enfant-m|Il a soif, papa.
+enfant-m|Je veux qu'il boive.
+papa|On le fait ensemble.
+papa|Avec un adulte.
+papa|On est doux.
+narrateur|En ce moment, Amir tient le bol avec papa.
+narrateur|L'eau arrive, un filet, pas trop.
+narrateur|Le bol se pose sans bruit.
+narrateur|Minou lape, tout près.
+enfant-m|Il boit.
+papa|Premier soin.
+papa|On reste près de moi.
+narrateur|Plus tard, la porte du jardin s'ouvre.
+narrateur|L'air sent l'herbe et le grain.
+narrateur|Deux poules picorent près du grillage.
+narrateur|Leur abreuvoir est bas, presque vide.
+enfant-m|Elles aussi.
+enfant-m|Elles ont soif.
+papa|Même leçon.
+papa|Autre animal.
+papa|On verse avec un adulte ?
+enfant-m|Oui, papa.
+narrateur|Amir porte le seau avec papa.
+narrateur|Le seau tape sa jambe, tout léger.
+narrateur|Ils versent un peu d'eau.
+narrateur|Puis un peu de grain, tout doux.
+narrateur|Les poules viennent.
+papa|On recule.
+narrateur|Amir met les mains dans ses poches.
+narrateur|Il ne prend pas les poules.
+enfant-m|Deux soins.
+papa|Chat, puis poules.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1345,19 +1390,19 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
+          <t>Amir donne à boire ou à manger. Comment ?</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Amir donne à boire ou à manger. Comment ?</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
           <t>Jade donne à boire ou à manger. Comment ?</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jade donne à boire ou à manger. Comment ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Jade donne à boire ou à manger. Comment ?</t>
-        </is>
-      </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
           <t>avec papa</t>
@@ -1380,7 +1425,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Elle le fait avec un adulte. Elle est douce. Comment fait Jade ?</t>
+          <t>Il le fait avec un adulte. Il est doux. Comment fait Amir ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1422,14 +1467,14 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>slow</t>
         </is>
       </c>
       <c r="AA3" s="2" t="n">
         <v>0.9</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1501,10 +1546,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Jade donne à boire ou à manger. Comment ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Amir donne à boire ou à manger.
+narrateur|Comment ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1529,12 +1574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Jade a été douce. Avec papa. Pour le chat, puis pour les poules.</t>
+          <t>Minou, à la maison, se lèche encore. Au jardin, les poules boivent à tour de rôle. Les deux ont bu. Oui. Tu as été doux. Avec un adulte. Deux fois. Merci, Amir. Tu as vu la différence ? Le bol, et le seau. Et le même geste. Doux. Une poule secoue le bec. Une goutte tombe dans l'herbe. L'herbe la garde. Comme Minou, tout à l'heure. Même soif. Même soin. Amir reste près de papa. Le seau vide est léger maintenant. Il le porte jusqu'au perron.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Jade a été douce. &lt;emphasis level="moderate"&gt;avec&lt;/emphasis&gt; papa. Pour le chat, puis pour les poules.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Minou, à la maison, se lèche encore. Au jardin, les poules boivent à tour de rôle. Les deux ont bu. Oui. Tu as été doux. Avec un adulte. Deux fois. Merci, Amir. Tu as vu la différence ? Le bol, et le seau. Et le même geste. Doux. Une poule secoue le bec. Une goutte tombe dans l'herbe. L'herbe la garde. Comme Minou, tout à l'heure. Même soif. Même soin. Amir reste près de papa. Le seau vide est léger maintenant. Il le porte jusqu'au perron.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1597,7 +1642,7 @@
         <v>0.96</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1673,10 +1718,29 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Jade a été douce. Avec papa. Pour le chat, puis pour les poules.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Minou, à la maison, se lèche encore.
+narrateur|Au jardin, les poules boivent à tour de rôle.
+enfant-m|Les deux ont bu.
+papa|Oui.
+papa|Tu as été doux.
+papa|Avec un adulte.
+papa|Deux fois.
+papa|Merci, Amir.
+papa|Tu as vu la différence ?
+enfant-m|Le bol, et le seau.
+papa|Et le même geste.
+papa|Doux.
+narrateur|Une poule secoue le bec.
+narrateur|Une goutte tombe dans l'herbe.
+narrateur|L'herbe la garde.
+enfant-m|Comme Minou, tout à l'heure.
+papa|Même soif.
+papa|Même soin.
+narrateur|Amir reste près de papa.
+narrateur|Le seau vide est léger maintenant.
+narrateur|Il le porte jusqu'au perron.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1701,12 +1765,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Minou se lèche. Les poules picorent.</t>
+          <t>Ils rentrent. Le cacao a refroidi, un peu. Amir reprend une gorgée. Nous aussi, on boit. Oui. Chacun sa tasse, chacun sa gamelle. Minou s'est recouché au radiateur. Son ronron revient, bas. Dehors, une poule chante un petit coucou. Tu as soigné deux soifs. Avec toi. Avec un adulte. La vapeur n'est plus là. Il reste l'odeur du cacao, et du grain. On range le seau près des bottes ? Oui. Le seau trouve sa place. Le bois du perron est sec.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Minou se lèche. Les poules picorent.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Ils rentrent. Le cacao a refroidi, un peu. Amir reprend une gorgée. Nous aussi, on boit. Oui. Chacun sa tasse, chacun sa gamelle. Minou s'est recouché au radiateur. Son ronron revient, bas. Dehors, une poule chante un petit coucou. Tu as soigné deux soifs. Avec toi. Avec un adulte. La vapeur n'est plus là. Il reste l'odeur du cacao, et du grain. On range le seau près des bottes ? Oui. Le seau trouve sa place. Le bois du perron est sec.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1769,7 +1833,7 @@
         <v>0.96</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1837,10 +1901,26 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Minou se lèche. Les poules picorent.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Ils rentrent.
+narrateur|Le cacao a refroidi, un peu.
+narrateur|Amir reprend une gorgée.
+enfant-m|Nous aussi, on boit.
+papa|Oui.
+papa|Chacun sa tasse, chacun sa gamelle.
+narrateur|Minou s'est recouché au radiateur.
+narrateur|Son ronron revient, bas.
+narrateur|Dehors, une poule chante un petit coucou.
+papa|Tu as soigné deux soifs.
+enfant-m|Avec toi.
+papa|Avec un adulte.
+narrateur|La vapeur n'est plus là.
+narrateur|Il reste l'odeur du cacao, et du grain.
+papa|On range le seau près des bottes ?
+enfant-m|Oui.
+narrateur|Le seau trouve sa place.
+narrateur|Le bois du perron est sec.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1865,12 +1945,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Minou a bu. Les poules aussi. Deux soins, tout doux. Une plume reste collée au grillage. Le matin sent encore le cacao.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Minou a bu. Les poules aussi. Deux soins, tout doux. Une plume reste collée au grillage. Le matin sent encore le cacao.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1933,7 +2013,7 @@
         <v>0.92</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2005,10 +2085,13 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|Minou a bu.
+enfant-m|Les poules aussi.
+papa|Deux soins, tout doux.
+narrateur|Une plume reste collée au grillage.
+narrateur|Le matin sent encore le cacao.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2027,7 +2110,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2065,6 +2148,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>maison puis jardin</t>
+          <t>cuisine puis jardin, matin de cacao</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jade, papa</t>
+          <t>Amir, papa</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
+++ b/stories/arbres/ATOM-VIV.ANI.003-03.xlsx
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Deux soifs, deux soins</t>
+          <t>L'eau de la chèvre</t>
         </is>
       </c>
     </row>
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine puis jardin, matin de cacao</t>
+          <t>alpage en fin de jour, cloche lointaine, pain, seau</t>
         </is>
       </c>
     </row>
@@ -841,7 +841,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Amir veut soigner deux soifs: Minou d'abord, puis les poules. Avec papa, doux, deux fois.</t>
+          <t>Amir veut que la chèvre boive, pour la regarder manger son pain. Le seau est vide. Avec papa, ils versent. Le chien halète, lui aussi. Ils remplissent son bol.</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur du cacao sent le matin. Elle monte en petit nuage au-dessus de la tasse. Le bois de la table est encore froid. Bois un peu, Amir. C'est chaud. Un miaulement arrive du radiateur. Minou le chat s'étire. Sa gamelle, près du buffet, est sèche. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Amir tient le bol avec papa. L'eau arrive, un filet, pas trop. Le bol se pose sans bruit. Minou lape, tout près. Il boit. Premier soin. On reste près de moi. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe et le grain. Deux poules picorent près du grillage. Leur abreuvoir est bas, presque vide. Elles aussi. Elles ont soif. Même leçon. Autre animal. On verse avec un adulte ? Oui, papa. Amir porte le seau avec papa. Le seau tape sa jambe, tout léger. Ils versent un peu d'eau. Puis un peu de grain, tout doux. Les poules viennent. On recule. Amir met les mains dans ses poches. Il ne prend pas les poules. Deux soins. Chat, puis poules.</t>
+          <t>L'herbe de l'alpage sent le foin chaud. Une cloche tinte, très loin. Le pain de la musette est encore tiède. Un seau de fer brille près du muret. Tu as vu la chèvre, Amir ? Elle a la barbe, papa. Elle a aussi soif, je crois. Le seau est presque vide. Une croûte sèche au fond. Je veux qu'elle boive. Pour la regarder, avec mon pain. On verse ensemble ? Oui. En ce moment, Amir tient l'anse avec papa. Le fer est chaud, un peu rêche. Ils penchent tout doux vers l'auge. L'eau arrive, un filet, pas trop. Elle vient. On recule un peu. La chèvre avance, tout prudent. Sa langue tape l'eau, toute rapide. Elle boit. Oui. Merci, Amir. Amir croque son pain. Le pain sent le foin, maintenant. Un chien halète près du muret. Sa langue est longue, toute rose. Son bol de terre est sec, tout blanc. Lui aussi. Il a soif. Tu as vu sa langue ? Oui. On lui en met ? Ensemble, encore. Ils portent le seau, plus léger. Un peu d'eau reste, assez pour le bol. Amir pose deux mains, papa aussi. Le filet tombe, tout lent, au centre. Le chien lape, tout près, tout bruyant. Il boit, lui aussi. Oui. Il avait soif. Une goutte tombe dans l'herbe. L'herbe la garde, sombre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>La vapeur du cacao sent le matin. Elle monte en petit nuage au-dessus de la tasse. Le bois de la table est encore froid. Bois un peu, Amir. C'est chaud. Un miaulement arrive du radiateur. Minou le chat s'étire. Sa gamelle, près du buffet, est sèche. Il a soif, papa. Je veux qu'il boive. On le fait ensemble. Avec un adulte. On est doux. En ce moment, Amir tient le bol avec papa. L'eau arrive, un filet, pas trop. Le bol se pose sans bruit. Minou lape, tout près. Il boit. Premier soin. On reste près de moi. Plus tard, la porte du jardin s'ouvre. L'air sent l'herbe et le grain. Deux poules picorent près du grillage. Leur abreuvoir est bas, presque vide. Elles aussi. Elles ont soif. Même leçon. Autre animal. On verse avec un adulte ? Oui, papa. Amir porte le seau avec papa. Le seau tape sa jambe, tout léger. Ils versent un peu d'eau. Puis un peu de grain, tout doux. Les poules viennent. On recule. Amir met les mains dans ses poches. Il ne prend pas les poules. Deux soins. Chat, puis poules.</t>
+          <t>L'herbe de l'alpage sent le foin chaud. Une cloche tinte, très loin. Le pain de la musette est encore tiède. Un seau de fer brille près du muret. Tu as vu la chèvre, Amir ? Elle a la barbe, papa. Elle a aussi soif, je crois. Le seau est presque vide. Une croûte sèche au fond. Je veux qu'elle boive. Pour la regarder, avec mon pain. On verse ensemble ? Oui. En ce moment, Amir tient l'anse avec papa. Le fer est chaud, un peu rêche. Ils penchent tout doux vers l'auge. L'eau arrive, un filet, pas trop. Elle vient. On recule un peu. La chèvre avance, tout prudent. Sa langue tape l'eau, toute rapide. Elle boit. Oui. Merci, Amir. Amir croque son pain. Le pain sent le foin, maintenant. Un chien halète près du muret. Sa langue est longue, toute rose. Son bol de terre est sec, tout blanc. Lui aussi. Il a soif. Tu as vu sa langue ? Oui. On lui en met ? Ensemble, encore. Ils portent le seau, plus léger. Un peu d'eau reste, assez pour le bol. Amir pose deux mains, papa aussi. Le filet tombe, tout lent, au centre. Le chien lape, tout près, tout bruyant. Il boit, lui aussi. Oui. Il avait soif. Une goutte tombe dans l'herbe. L'herbe la garde, sombre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1324,46 +1324,51 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|La vapeur du cacao sent le matin.
-narrateur|Elle monte en petit nuage au-dessus de la tasse.
-narrateur|Le bois de la table est encore froid.
-papa|Bois un peu, Amir.
-enfant-m|C'est chaud.
-narrateur|Un miaulement arrive du radiateur.
-narrateur|Minou le chat s'étire.
-narrateur|Sa gamelle, près du buffet, est sèche.
-enfant-m|Il a soif, papa.
-enfant-m|Je veux qu'il boive.
-papa|On le fait ensemble.
-papa|Avec un adulte.
-papa|On est doux.
-narrateur|En ce moment, Amir tient le bol avec papa.
+          <t>narrateur|L'herbe de l'alpage sent le foin chaud.
+narrateur|Une cloche tinte, très loin.
+narrateur|Le pain de la musette est encore tiède.
+narrateur|Un seau de fer brille près du muret.
+papa|Tu as vu la chèvre, Amir ?
+enfant-m|Elle a la barbe, papa.
+papa|Elle a aussi soif, je crois.
+narrateur|Le seau est presque vide.
+narrateur|Une croûte sèche au fond.
+enfant-m|Je veux qu'elle boive.
+enfant-m|Pour la regarder, avec mon pain.
+papa|On verse ensemble ?
+enfant-m|Oui.
+narrateur|En ce moment, Amir tient l'anse avec papa.
+narrateur|Le fer est chaud, un peu rêche.
+narrateur|Ils penchent tout doux vers l'auge.
 narrateur|L'eau arrive, un filet, pas trop.
-narrateur|Le bol se pose sans bruit.
-narrateur|Minou lape, tout près.
-enfant-m|Il boit.
-papa|Premier soin.
-papa|On reste près de moi.
-narrateur|Plus tard, la porte du jardin s'ouvre.
-narrateur|L'air sent l'herbe et le grain.
-narrateur|Deux poules picorent près du grillage.
-narrateur|Leur abreuvoir est bas, presque vide.
-enfant-m|Elles aussi.
-enfant-m|Elles ont soif.
-papa|Même leçon.
-papa|Autre animal.
-papa|On verse avec un adulte ?
-enfant-m|Oui, papa.
-narrateur|Amir porte le seau avec papa.
-narrateur|Le seau tape sa jambe, tout léger.
-narrateur|Ils versent un peu d'eau.
-narrateur|Puis un peu de grain, tout doux.
-narrateur|Les poules viennent.
-papa|On recule.
-narrateur|Amir met les mains dans ses poches.
-narrateur|Il ne prend pas les poules.
-enfant-m|Deux soins.
-papa|Chat, puis poules.</t>
+enfant-m|Elle vient.
+papa|On recule un peu.
+narrateur|La chèvre avance, tout prudent.
+narrateur|Sa langue tape l'eau, toute rapide.
+enfant-m|Elle boit.
+papa|Oui.
+papa|Merci, Amir.
+narrateur|Amir croque son pain.
+narrateur|Le pain sent le foin, maintenant.
+narrateur|Un chien halète près du muret.
+narrateur|Sa langue est longue, toute rose.
+narrateur|Son bol de terre est sec, tout blanc.
+enfant-m|Lui aussi.
+enfant-m|Il a soif.
+papa|Tu as vu sa langue ?
+enfant-m|Oui.
+enfant-m|On lui en met ?
+papa|Ensemble, encore.
+narrateur|Ils portent le seau, plus léger.
+narrateur|Un peu d'eau reste, assez pour le bol.
+narrateur|Amir pose deux mains, papa aussi.
+narrateur|Le filet tombe, tout lent, au centre.
+narrateur|Le chien lape, tout près, tout bruyant.
+enfant-m|Il boit, lui aussi.
+papa|Oui.
+papa|Il avait soif.
+narrateur|Une goutte tombe dans l'herbe.
+narrateur|L'herbe la garde, sombre.</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1395,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amir donne à boire ou à manger. Comment ?</t>
+          <t>Amir donne à boire. Comment ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Amir donne à boire ou à manger. Comment ?</t>
+          <t>Amir donne à boire. Comment ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1425,7 +1430,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Il le fait avec un adulte. Il est doux. Comment fait Amir ?</t>
+          <t>Amir tient le seau. Comment donne-t-il à boire ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1546,7 +1551,7 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amir donne à boire ou à manger.
+          <t>narrateur|Amir donne à boire.
 narrateur|Comment ?</t>
         </is>
       </c>
@@ -1574,12 +1579,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Minou, à la maison, se lèche encore. Au jardin, les poules boivent à tour de rôle. Les deux ont bu. Oui. Tu as été doux. Avec un adulte. Deux fois. Merci, Amir. Tu as vu la différence ? Le bol, et le seau. Et le même geste. Doux. Une poule secoue le bec. Une goutte tombe dans l'herbe. L'herbe la garde. Comme Minou, tout à l'heure. Même soif. Même soin. Amir reste près de papa. Le seau vide est léger maintenant. Il le porte jusqu'au perron.</t>
+          <t>La chèvre se lèche la barbe. Le chien se couche près du bol. Les deux ont bu. Oui. Tu as tenu le seau avec moi. Tout doux. Merci, Amir. Tu as vu la différence ? L'auge, et le bol. Et la même eau. La cloche tinte encore, plus bas. Le pain a une marque de dent. Il goûte l'herbe. Tu en donnes à la chèvre ? Un tout petit bout. La chèvre le prend, toute douce. Ses dents font un petit bruit. On reste un peu ? Un peu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>Minou, à la maison, se lèche encore. Au jardin, les poules boivent à tour de rôle. Les deux ont bu. Oui. Tu as été doux. Avec un adulte. Deux fois. Merci, Amir. Tu as vu la différence ? Le bol, et le seau. Et le même geste. Doux. Une poule secoue le bec. Une goutte tombe dans l'herbe. L'herbe la garde. Comme Minou, tout à l'heure. Même soif. Même soin. Amir reste près de papa. Le seau vide est léger maintenant. Il le porte jusqu'au perron.</t>
+          <t>La chèvre se lèche la barbe. Le chien se couche près du bol. Les deux ont bu. Oui. Tu as tenu le seau avec moi. Tout doux. Merci, Amir. Tu as vu la différence ? L'auge, et le bol. Et la même eau. La cloche tinte encore, plus bas. Le pain a une marque de dent. Il goûte l'herbe. Tu en donnes à la chèvre ? Un tout petit bout. La chèvre le prend, toute douce. Ses dents font un petit bruit. On reste un peu ? Un peu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1718,27 +1723,25 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Minou, à la maison, se lèche encore.
-narrateur|Au jardin, les poules boivent à tour de rôle.
+          <t>narrateur|La chèvre se lèche la barbe.
+narrateur|Le chien se couche près du bol.
 enfant-m|Les deux ont bu.
 papa|Oui.
-papa|Tu as été doux.
-papa|Avec un adulte.
-papa|Deux fois.
+papa|Tu as tenu le seau avec moi.
+papa|Tout doux.
 papa|Merci, Amir.
 papa|Tu as vu la différence ?
-enfant-m|Le bol, et le seau.
-papa|Et le même geste.
-papa|Doux.
-narrateur|Une poule secoue le bec.
-narrateur|Une goutte tombe dans l'herbe.
-narrateur|L'herbe la garde.
-enfant-m|Comme Minou, tout à l'heure.
-papa|Même soif.
-papa|Même soin.
-narrateur|Amir reste près de papa.
-narrateur|Le seau vide est léger maintenant.
-narrateur|Il le porte jusqu'au perron.</t>
+enfant-m|L'auge, et le bol.
+papa|Et la même eau.
+narrateur|La cloche tinte encore, plus bas.
+narrateur|Le pain a une marque de dent.
+enfant-m|Il goûte l'herbe.
+papa|Tu en donnes à la chèvre ?
+enfant-m|Un tout petit bout.
+narrateur|La chèvre le prend, toute douce.
+narrateur|Ses dents font un petit bruit.
+papa|On reste un peu ?
+enfant-m|Un peu.</t>
         </is>
       </c>
     </row>
@@ -1765,12 +1768,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent. Le cacao a refroidi, un peu. Amir reprend une gorgée. Nous aussi, on boit. Oui. Chacun sa tasse, chacun sa gamelle. Minou s'est recouché au radiateur. Son ronron revient, bas. Dehors, une poule chante un petit coucou. Tu as soigné deux soifs. Avec toi. Avec un adulte. La vapeur n'est plus là. Il reste l'odeur du cacao, et du grain. On range le seau près des bottes ? Oui. Le seau trouve sa place. Le bois du perron est sec.</t>
+          <t>Le soleil glisse derrière le muret. L'ombre est longue, plus froide. On reprend la musette ? Oui. Ils ont bu. Oui. Toi aussi, tu as bu l'air du soir. Le seau vide est léger, maintenant. Il tape la jambe, tout doux. On le pose près des bottes ? Oui. Le chien ronfle déjà, un peu. La chèvre broute, calme.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>Ils rentrent. Le cacao a refroidi, un peu. Amir reprend une gorgée. Nous aussi, on boit. Oui. Chacun sa tasse, chacun sa gamelle. Minou s'est recouché au radiateur. Son ronron revient, bas. Dehors, une poule chante un petit coucou. Tu as soigné deux soifs. Avec toi. Avec un adulte. La vapeur n'est plus là. Il reste l'odeur du cacao, et du grain. On range le seau près des bottes ? Oui. Le seau trouve sa place. Le bois du perron est sec.</t>
+          <t>Le soleil glisse derrière le muret. L'ombre est longue, plus froide. On reprend la musette ? Oui. Ils ont bu. Oui. Toi aussi, tu as bu l'air du soir. Le seau vide est léger, maintenant. Il tape la jambe, tout doux. On le pose près des bottes ? Oui. Le chien ronfle déjà, un peu. La chèvre broute, calme.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1901,24 +1904,19 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Ils rentrent.
-narrateur|Le cacao a refroidi, un peu.
-narrateur|Amir reprend une gorgée.
-enfant-m|Nous aussi, on boit.
+          <t>narrateur|Le soleil glisse derrière le muret.
+narrateur|L'ombre est longue, plus froide.
+papa|On reprend la musette ?
+enfant-m|Oui.
+enfant-m|Ils ont bu.
 papa|Oui.
-papa|Chacun sa tasse, chacun sa gamelle.
-narrateur|Minou s'est recouché au radiateur.
-narrateur|Son ronron revient, bas.
-narrateur|Dehors, une poule chante un petit coucou.
-papa|Tu as soigné deux soifs.
-enfant-m|Avec toi.
-papa|Avec un adulte.
-narrateur|La vapeur n'est plus là.
-narrateur|Il reste l'odeur du cacao, et du grain.
-papa|On range le seau près des bottes ?
+papa|Toi aussi, tu as bu l'air du soir.
+narrateur|Le seau vide est léger, maintenant.
+narrateur|Il tape la jambe, tout doux.
+papa|On le pose près des bottes ?
 enfant-m|Oui.
-narrateur|Le seau trouve sa place.
-narrateur|Le bois du perron est sec.</t>
+narrateur|Le chien ronfle déjà, un peu.
+narrateur|La chèvre broute, calme.</t>
         </is>
       </c>
     </row>
@@ -1945,12 +1943,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Minou a bu. Les poules aussi. Deux soins, tout doux. Une plume reste collée au grillage. Le matin sent encore le cacao.</t>
+          <t>Une goutte reste dans l'herbe. Elle a bu. Le chien aussi. Oui. Le pain sent encore le foin chaud. La cloche tinte, très loin.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>Minou a bu. Les poules aussi. Deux soins, tout doux. Une plume reste collée au grillage. Le matin sent encore le cacao.</t>
+          <t>Une goutte reste dans l'herbe. Elle a bu. Le chien aussi. Oui. Le pain sent encore le foin chaud. La cloche tinte, très loin.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2085,11 +2083,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>enfant-m|Minou a bu.
-enfant-m|Les poules aussi.
-papa|Deux soins, tout doux.
-narrateur|Une plume reste collée au grillage.
-narrateur|Le matin sent encore le cacao.</t>
+          <t>narrateur|Une goutte reste dans l'herbe.
+enfant-m|Elle a bu.
+enfant-m|Le chien aussi.
+papa|Oui.
+narrateur|Le pain sent encore le foin chaud.
+narrateur|La cloche tinte, très loin.</t>
         </is>
       </c>
     </row>
@@ -2110,7 +2109,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2153,6 +2152,13 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
